--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484285_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484285_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9501</v>
+        <v>8.429</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3661</v>
+        <v>5.7905</v>
       </c>
       <c r="F2" t="n">
-        <v>2.584</v>
+        <v>2.6385</v>
       </c>
       <c r="G2" t="n">
         <v>3.9098</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1866</v>
+        <v>0.2923</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5915</v>
+        <v>-0.1671</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4049</v>
+        <v>0.4593</v>
       </c>
       <c r="V2" t="n">
         <v>1.8828</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8188</v>
+        <v>7.374</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1958</v>
+        <v>5.5237</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6229</v>
+        <v>1.8503</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3056</v>
+        <v>4.2181</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9964</v>
+        <v>1.8442</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3091</v>
+        <v>2.3739</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7161</v>
+        <v>5.3264</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5416</v>
+        <v>2.6823</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1745</v>
+        <v>2.6441</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5895</v>
+        <v>-1.1083</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4549</v>
+        <v>-0.838</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1346</v>
+        <v>-0.2702</v>
       </c>
       <c r="P3" t="n">
         <v>0.9767</v>
@@ -688,28 +688,28 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8686</v>
+        <v>0.0192</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7886</v>
+        <v>-0.3218</v>
       </c>
       <c r="U3" t="n">
-        <v>1.08</v>
+        <v>0.341</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3321</v>
+        <v>2.16</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3321</v>
+        <v>1.4959</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.0664</v>
+        <v>6.3197</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9982</v>
+        <v>2.9418</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0682</v>
+        <v>3.3778</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2181</v>
+        <v>4.3056</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8442</v>
+        <v>2.9964</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3739</v>
+        <v>1.3091</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3264</v>
+        <v>3.7161</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6823</v>
+        <v>2.5416</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6441</v>
+        <v>1.1745</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1083</v>
+        <v>0.5895</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.838</v>
+        <v>0.4549</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2702</v>
+        <v>0.1346</v>
       </c>
       <c r="P4" t="n">
         <v>0.9767</v>
@@ -766,22 +766,22 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2884</v>
+        <v>1.3695</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.5346</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5589</v>
+        <v>0.8349</v>
       </c>
       <c r="V4" t="n">
-        <v>2.16</v>
+        <v>-0.3321</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>-0.3321</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.0143</v>
+        <v>5.2854</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0082</v>
+        <v>5.3609</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0062</v>
+        <v>-0.0755</v>
       </c>
       <c r="G5" t="n">
         <v>5.5336</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.1657</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8173</v>
+        <v>0.17</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0774</v>
+        <v>-0.0043</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6093</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.639</v>
+        <v>4.9562</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8355</v>
+        <v>1.0983</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8035</v>
+        <v>3.8579</v>
       </c>
       <c r="G6" t="n">
         <v>2.6632</v>
@@ -922,13 +922,13 @@
         <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1711</v>
+        <v>0.4884</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2337</v>
+        <v>0.029</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4049</v>
+        <v>0.4593</v>
       </c>
       <c r="V6" t="n">
         <v>1.2186</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0539</v>
+        <v>3.3789</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8383</v>
+        <v>1.9999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2156</v>
+        <v>1.379</v>
       </c>
       <c r="G7" t="n">
         <v>1.6518</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.356</v>
+        <v>-0.031</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2283</v>
+        <v>-0.0667</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1277</v>
+        <v>0.0357</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1854</v>
+        <v>2.2031</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5353</v>
+        <v>-0.2725</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7207</v>
+        <v>2.4756</v>
       </c>
       <c r="G8" t="n">
         <v>0.1066</v>
@@ -1078,13 +1078,13 @@
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5161</v>
+        <v>0.5337</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2943</v>
+        <v>-0.0315</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8104</v>
+        <v>0.5653</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2839</v>
+        <v>1.6634</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8954</v>
+        <v>1.0571</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3885</v>
+        <v>0.6063</v>
       </c>
       <c r="G9" t="n">
         <v>1.2597</v>
@@ -1156,13 +1156,13 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1711</v>
+        <v>0.2084</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3494</v>
+        <v>-0.1877</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1782</v>
+        <v>0.3961</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2252</v>
+        <v>1.4625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7822</v>
+        <v>0.8833</v>
       </c>
       <c r="F10" t="n">
-        <v>0.443</v>
+        <v>0.5792</v>
       </c>
       <c r="G10" t="n">
         <v>0.3354</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7511</v>
+        <v>-0.5138</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1678</v>
+        <v>-0.0667</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5833</v>
+        <v>-0.4471</v>
       </c>
       <c r="V10" t="n">
         <v>0.6642</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.155</v>
+        <v>0.2561</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1351</v>
+        <v>-1.034</v>
       </c>
       <c r="F11" t="n">
         <v>1.2901</v>
@@ -1312,10 +1312,10 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6603</v>
+        <v>0.7614</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1127</v>
+        <v>-0.0116</v>
       </c>
       <c r="U11" t="n">
         <v>0.773</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.622</v>
+        <v>-0.4317</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6481</v>
+        <v>-1.6967</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0261</v>
+        <v>1.2649</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2947</v>
+        <v>-1.7049</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08309999999999999</v>
+        <v>-0.2758</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3778</v>
+        <v>-1.4291</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4497</v>
+        <v>-1.4154</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2878</v>
+        <v>-0.1215</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1619</v>
+        <v>-1.2939</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7443</v>
+        <v>-0.2895</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2047</v>
+        <v>-0.1542</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5397</v>
+        <v>-0.1352</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1453</v>
+        <v>-0.2896</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.121</v>
+        <v>-0.2812</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2663</v>
+        <v>-0.0083</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1552</v>
+        <v>-0.6765</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2022</v>
+        <v>-0.6481</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0471</v>
+        <v>-0.0284</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7049</v>
+        <v>-0.2947</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2758</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4291</v>
+        <v>-0.3778</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4154</v>
+        <v>0.4497</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1215</v>
+        <v>0.2878</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2939</v>
+        <v>0.1619</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2895</v>
+        <v>-0.7443</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1542</v>
+        <v>-0.2047</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1352</v>
+        <v>-0.5397</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.013</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.121</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2262</v>
+        <v>0.2118</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>39.6148</v>
+        <v>40.2201</v>
       </c>
       <c r="E14" t="n">
-        <v>20.399</v>
+        <v>21.0042</v>
       </c>
       <c r="F14" t="n">
-        <v>19.2159</v>
+        <v>19.2157</v>
       </c>
       <c r="G14" t="n">
         <v>21.67420000000001</v>
@@ -1525,10 +1525,10 @@
         <v>17.8181</v>
       </c>
       <c r="L14" t="n">
-        <v>8.101099999999999</v>
+        <v>8.101100000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.244800000000001</v>
+        <v>-4.2448</v>
       </c>
       <c r="N14" t="n">
         <v>-1.5423</v>
@@ -1546,19 +1546,19 @@
         <v>20.5111</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4899</v>
+        <v>3.095</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1269</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6168</v>
+        <v>3.6167</v>
       </c>
       <c r="V14" t="n">
         <v>4.707000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>5.374</v>
+        <v>5.374000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-0.6668999999999998</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.6087</v>
+        <v>-1.0602</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3296</v>
+        <v>-0.0262</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2791</v>
+        <v>-1.034</v>
       </c>
       <c r="G15" t="n">
         <v>2.8279</v>
@@ -1624,13 +1624,13 @@
         <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8738</v>
+        <v>-0.3254</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5915</v>
+        <v>-0.2881</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2824</v>
+        <v>-0.0373</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2186</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0497</v>
+        <v>-1.8205</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3472</v>
+        <v>-0.669</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7025</v>
+        <v>-1.1515</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3331</v>
+        <v>-2.256</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.429</v>
+        <v>-1.2039</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9041</v>
+        <v>-1.0521</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1837</v>
+        <v>0.1914</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1433</v>
+        <v>0.1637</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>0.0276</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5168</v>
+        <v>-2.4474</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5723</v>
+        <v>-1.3676</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9445</v>
+        <v>-1.0797</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.498</v>
+        <v>0.4355</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5309</v>
+        <v>0.1164</v>
       </c>
       <c r="U16" t="n">
-        <v>0.033</v>
+        <v>0.3191</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1266</v>
+        <v>-1.9486</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5679</v>
+        <v>-0.2461</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5587</v>
+        <v>-1.7025</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.256</v>
+        <v>-2.3331</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2039</v>
+        <v>-1.429</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0521</v>
+        <v>-0.9041</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1914</v>
+        <v>0.1837</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1637</v>
+        <v>0.1433</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0276</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4474</v>
+        <v>-2.5168</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3676</v>
+        <v>-1.5723</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0797</v>
+        <v>-0.9445</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1294</v>
+        <v>-0.3968</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2175</v>
+        <v>-0.4298</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0881</v>
+        <v>0.033</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.8104</v>
+        <v>-3.4798</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1578</v>
+        <v>0.4611</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.9682</v>
+        <v>-3.9409</v>
       </c>
       <c r="G18" t="n">
         <v>1.1759</v>
@@ -1858,13 +1858,13 @@
         <v>1.3674</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2282</v>
+        <v>-0.8976</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3315</v>
+        <v>-1.0282</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1033</v>
+        <v>0.1305</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2186</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8666</v>
+        <v>-5.1228</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.829</v>
+        <v>-3.8401</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0376</v>
+        <v>-1.2827</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7755</v>
@@ -1936,13 +1936,13 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4131</v>
+        <v>0.1568</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9467</v>
+        <v>-0.0645</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4664</v>
+        <v>0.2213</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9414</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2784</v>
+        <v>-5.3846</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8119</v>
+        <v>-2.2164</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4665</v>
+        <v>-3.1683</v>
       </c>
       <c r="G20" t="n">
         <v>-3.9311</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1448</v>
+        <v>0.0386</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3469</v>
+        <v>-0.0576</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.202</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8828</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>M. PACÍFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2965</v>
+        <v>-5.9746</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2539</v>
+        <v>-3.1576</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0425</v>
+        <v>-2.817</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.4811</v>
+        <v>-5.1251</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.6716</v>
+        <v>-1.2003</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8095</v>
+        <v>-3.9248</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2185</v>
+        <v>-1.7986</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9965000000000001</v>
+        <v>0.1023</v>
       </c>
       <c r="L21" t="n">
-        <v>1.215</v>
+        <v>-1.9009</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.6996</v>
+        <v>-3.3265</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.6751</v>
+        <v>-1.3026</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0245</v>
+        <v>-2.0239</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7252</v>
+        <v>-0.1816</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7647</v>
+        <v>-0.3823</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0394</v>
+        <v>0.2008</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6228</v>
+        <v>-6.3911</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5621</v>
+        <v>-3.4562</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0607</v>
+        <v>-2.935</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.1251</v>
+        <v>-4.4811</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2003</v>
+        <v>-3.6716</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.9248</v>
+        <v>-0.8095</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7986</v>
+        <v>0.2185</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1023</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9009</v>
+        <v>1.215</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3265</v>
+        <v>-4.6996</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3026</v>
+        <v>-2.6751</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0239</v>
+        <v>-2.0245</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8298</v>
+        <v>-0.8199</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.9669</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.043</v>
+        <v>0.147</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9552</v>
+        <v>-7.7584</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.6721</v>
+        <v>-6.0654</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2831</v>
+        <v>-1.693</v>
       </c>
       <c r="G23" t="n">
         <v>-4.776</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0221</v>
+        <v>0.1747</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1224</v>
+        <v>-0.5157</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1003</v>
+        <v>0.6904</v>
       </c>
       <c r="V23" t="n">
         <v>0.5545</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-39.6149</v>
+        <v>-38.9406</v>
       </c>
       <c r="E24" t="n">
         <v>-19.2159</v>
       </c>
       <c r="F24" t="n">
-        <v>-20.3989</v>
+        <v>-19.7249</v>
       </c>
       <c r="G24" t="n">
         <v>-21.6741</v>
@@ -2326,13 +2326,13 @@
         <v>9.767099999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.4898</v>
+        <v>-1.8157</v>
       </c>
       <c r="T24" t="n">
         <v>-3.6167</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1269</v>
+        <v>1.801</v>
       </c>
       <c r="V24" t="n">
         <v>-4.7069</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484285_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484285_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +653,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.374</v>
+        <v>6.4601</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5237</v>
+        <v>4.6097</v>
       </c>
       <c r="F3" t="n">
         <v>1.8503</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2181</v>
+        <v>3.3041</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8442</v>
+        <v>1.5372</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3739</v>
+        <v>1.7669</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3264</v>
+        <v>4.4124</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6823</v>
+        <v>2.3753</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6441</v>
+        <v>2.0371</v>
       </c>
       <c r="M3" t="n">
         <v>-1.1083</v>
@@ -704,12 +714,17 @@
       </c>
       <c r="X3" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,28 +736,28 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3197</v>
+        <v>6.0127</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9418</v>
+        <v>2.6349</v>
       </c>
       <c r="F4" t="n">
         <v>3.3778</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3056</v>
+        <v>3.9986</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9964</v>
+        <v>2.6895</v>
       </c>
       <c r="I4" t="n">
         <v>1.3091</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7161</v>
+        <v>3.4091</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5416</v>
+        <v>2.2346</v>
       </c>
       <c r="L4" t="n">
         <v>1.1745</v>
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1250,12 +1295,17 @@
       </c>
       <c r="X10" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. MAYO SCHWANDT</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2561</v>
+        <v>0.914</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.034</v>
+        <v>0.914</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2901</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.31</v>
+        <v>0.914</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6332</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9431</v>
+        <v>0.607</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0445</v>
+        <v>0.914</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7176</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6731</v>
+        <v>0.607</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3544</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7614</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0116</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1400,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4317</v>
+        <v>0.914</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6967</v>
+        <v>0.914</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2649</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7049</v>
+        <v>0.914</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2758</v>
+        <v>0.307</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4291</v>
+        <v>0.607</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4154</v>
+        <v>0.914</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1215</v>
+        <v>0.307</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2939</v>
+        <v>0.607</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2895</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1352</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2896</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2812</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0083</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1406,12 +1461,17 @@
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.6765</v>
+        <v>0.307</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6481</v>
+        <v>0.307</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0284</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2947</v>
+        <v>0.307</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3778</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4497</v>
+        <v>0.307</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2878</v>
+        <v>0.307</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7443</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5397</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09080000000000001</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2118</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MAYO SCHWANDT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,214 +1566,224 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>40.2201</v>
+        <v>0.2561</v>
       </c>
       <c r="E14" t="n">
-        <v>21.0042</v>
+        <v>-1.034</v>
       </c>
       <c r="F14" t="n">
-        <v>19.2157</v>
+        <v>1.2901</v>
       </c>
       <c r="G14" t="n">
-        <v>21.67420000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="H14" t="n">
-        <v>16.2754</v>
+        <v>0.6332</v>
       </c>
       <c r="I14" t="n">
-        <v>5.398800000000001</v>
+        <v>-0.9431</v>
       </c>
       <c r="J14" t="n">
-        <v>25.9191</v>
+        <v>0.0445</v>
       </c>
       <c r="K14" t="n">
-        <v>17.8181</v>
+        <v>0.7176</v>
       </c>
       <c r="L14" t="n">
-        <v>8.101100000000001</v>
+        <v>-0.6731</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.2448</v>
+        <v>-0.3544</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5423</v>
+        <v>-0.0844</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7024</v>
+        <v>-0.27</v>
       </c>
       <c r="P14" t="n">
-        <v>10.7437</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.766999999999999</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>20.5111</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>3.095</v>
+        <v>0.7614</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.0116</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6167</v>
+        <v>0.773</v>
       </c>
       <c r="V14" t="n">
-        <v>4.707000000000001</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>5.374000000000001</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6668999999999998</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0602</v>
+        <v>-0.6765</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0262</v>
+        <v>-0.6481</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.034</v>
+        <v>-0.0284</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8279</v>
+        <v>-0.2947</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2991</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1269</v>
+        <v>-0.3778</v>
       </c>
       <c r="J15" t="n">
-        <v>3.192</v>
+        <v>0.4497</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1433</v>
+        <v>0.2878</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0487</v>
+        <v>0.1619</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3641</v>
+        <v>-0.7443</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4423</v>
+        <v>-0.2047</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0782</v>
+        <v>-0.5397</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3441</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3254</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2881</v>
+        <v>-0.121</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0373</v>
+        <v>0.2118</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. LOPEZ SANCHEZ</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8205</v>
+        <v>-1.3457</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.669</v>
+        <v>-2.6106</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1515</v>
+        <v>1.2649</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.256</v>
+        <v>-2.6189</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2039</v>
+        <v>-0.5828</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0521</v>
+        <v>-2.0361</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1914</v>
+        <v>-2.3294</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1637</v>
+        <v>-0.4285</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0276</v>
+        <v>-1.9009</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4474</v>
+        <v>-0.2895</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3676</v>
+        <v>-0.1542</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0797</v>
+        <v>-0.1352</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4355</v>
+        <v>-0.2896</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1164</v>
+        <v>-0.2812</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3191</v>
+        <v>-0.0083</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1718,90 +1793,96 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C.B. CUARTE DE HUERVA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9486</v>
+        <v>40.22020000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2461</v>
+        <v>21.0044</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7025</v>
+        <v>19.2157</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.3331</v>
+        <v>21.6742</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.429</v>
+        <v>16.2755</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9041</v>
+        <v>5.3988</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1837</v>
+        <v>25.9191</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1433</v>
+        <v>17.8181</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>8.101099999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5168</v>
+        <v>-4.244800000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5723</v>
+        <v>-1.5423</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9445</v>
+        <v>-2.7024</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>10.7437</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-9.766999999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>20.5111</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3968</v>
+        <v>3.095</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4298</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.033</v>
+        <v>3.6167</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.707000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>5.374000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.6668999999999998</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4798</v>
+        <v>-1.0602</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4611</v>
+        <v>-0.0262</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.9409</v>
+        <v>-1.034</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1759</v>
+        <v>2.8279</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4193</v>
+        <v>-1.2991</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2434</v>
+        <v>4.1269</v>
       </c>
       <c r="J18" t="n">
-        <v>5.3962</v>
+        <v>3.192</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4804</v>
+        <v>0.1433</v>
       </c>
       <c r="L18" t="n">
-        <v>1.9157</v>
+        <v>3.0487</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.2202</v>
+        <v>-0.3641</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.0611</v>
+        <v>-1.4423</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1591</v>
+        <v>1.0782</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5395</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9069</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8976</v>
+        <v>-0.3254</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0282</v>
+        <v>-0.2881</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1305</v>
+        <v>-0.0373</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2186</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>O. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.1228</v>
+        <v>-1.8205</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8401</v>
+        <v>-0.669</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2827</v>
+        <v>-1.1515</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7755</v>
+        <v>-2.256</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.451</v>
+        <v>-1.2039</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3245</v>
+        <v>-1.0521</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1227</v>
+        <v>0.1914</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5296</v>
+        <v>0.1637</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6528</v>
+        <v>-2.4474</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9215</v>
+        <v>-1.3676</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2687</v>
+        <v>-1.0797</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1568</v>
+        <v>0.4355</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0645</v>
+        <v>0.1164</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2213</v>
+        <v>0.3191</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.3846</v>
+        <v>-1.9486</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2164</v>
+        <v>-0.2461</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1683</v>
+        <v>-1.7025</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.9311</v>
+        <v>-2.3331</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.3101</v>
+        <v>-1.429</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.621</v>
+        <v>-0.9041</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7951</v>
+        <v>0.1837</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8494</v>
+        <v>0.1433</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0543</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.136</v>
+        <v>-2.5168</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4607</v>
+        <v>-1.5723</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6753</v>
+        <v>-0.9445</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0386</v>
+        <v>-0.3968</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0576</v>
+        <v>-0.4298</v>
       </c>
       <c r="U20" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PACÍFICO CANTARELLI</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9746</v>
+        <v>-3.4798</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1576</v>
+        <v>0.4611</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.817</v>
+        <v>-3.9409</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.1251</v>
+        <v>1.1759</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2003</v>
+        <v>1.4193</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.9248</v>
+        <v>-0.2434</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7986</v>
+        <v>5.3962</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1023</v>
+        <v>3.4804</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9009</v>
+        <v>1.9157</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3265</v>
+        <v>-4.2202</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3026</v>
+        <v>-2.0611</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0239</v>
+        <v>-2.1591</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1816</v>
+        <v>-0.8976</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3823</v>
+        <v>-1.0282</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2008</v>
+        <v>0.1305</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3911</v>
+        <v>-5.1228</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4562</v>
+        <v>-3.8401</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.935</v>
+        <v>-1.2827</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.4811</v>
+        <v>-2.7755</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.6716</v>
+        <v>-2.451</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8095</v>
+        <v>-0.3245</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2185</v>
+        <v>-1.1227</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.5296</v>
       </c>
       <c r="L22" t="n">
-        <v>1.215</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.6996</v>
+        <v>-1.6528</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.6751</v>
+        <v>-1.9215</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0245</v>
+        <v>0.2687</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3674</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8199</v>
+        <v>0.1568</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9669</v>
+        <v>-0.0645</v>
       </c>
       <c r="U22" t="n">
-        <v>0.147</v>
+        <v>0.2213</v>
       </c>
       <c r="V22" t="n">
+        <v>-0.9414</v>
+      </c>
+      <c r="W22" t="n">
         <v>0.2772</v>
       </c>
-      <c r="W22" t="n">
-        <v>0.2224</v>
-      </c>
       <c r="X22" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.7584</v>
+        <v>-5.3846</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0654</v>
+        <v>-2.2164</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.693</v>
+        <v>-3.1683</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.776</v>
+        <v>-3.9311</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1298</v>
+        <v>-3.3101</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6463</v>
+        <v>-0.621</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2206</v>
+        <v>-0.7951</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1152</v>
+        <v>-0.8494</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1054</v>
+        <v>0.0543</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.5554</v>
+        <v>-3.136</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.0146</v>
+        <v>-2.4607</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5409</v>
+        <v>-0.6753</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.7115</v>
+        <v>0.3907</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1747</v>
+        <v>0.0386</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5157</v>
+        <v>-0.0576</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6904</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5545</v>
+        <v>-1.8828</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5545</v>
+        <v>-0.3869</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. PACIFICO CANTARELLI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-5.9746</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.1576</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.817</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-5.1251</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.2003</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.9248</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.7986</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.9009</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-3.3265</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.3026</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-2.0239</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.1816</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.3823</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. FERNANDEZ MANZANARES</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.3911</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.4562</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.935</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-4.4811</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.6716</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.8095</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2185</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.9965000000000001</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-4.6996</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-2.6751</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-2.0245</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.8199</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.9669</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>N. CLEDJO HOUNGUES</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-7.7584</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-6.0654</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.693</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.776</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.1298</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.6463</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.2206</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.1152</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.1054</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-3.5554</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-3.0146</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5409</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-3.7115</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1747</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.5157</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.6904</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484285_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. CUARTE DE HUERVA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-38.9406</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E27" t="n">
         <v>-19.2159</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F27" t="n">
         <v>-19.7249</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>-21.6741</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H27" t="n">
         <v>-16.2755</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I27" t="n">
         <v>-5.3988</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J27" t="n">
         <v>4.2448</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K27" t="n">
         <v>1.5423</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L27" t="n">
         <v>2.702300000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>-25.9188</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>-17.8178</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>-8.101000000000001</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>-10.7438</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-20.5109</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>9.767099999999999</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>-1.8157</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>-3.6167</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>1.801</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>-4.7069</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>0.6672</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-5.374000000000001</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
